--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487413_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487413_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.3174</v>
+        <v>6.9408</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0405</v>
+        <v>0.4234</v>
       </c>
       <c r="F2" t="n">
-        <v>6.2769</v>
+        <v>6.5174</v>
       </c>
       <c r="G2" t="n">
         <v>4.7863</v>
@@ -610,13 +610,13 @@
         <v>1.9585</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3145</v>
+        <v>0.9379</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1206</v>
+        <v>0.2623</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4351</v>
+        <v>0.6756</v>
       </c>
       <c r="V2" t="n">
         <v>1.2166</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.1883</v>
+        <v>5.4133</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.6966</v>
+        <v>-1.7231</v>
       </c>
       <c r="F3" t="n">
-        <v>7.8849</v>
+        <v>7.1364</v>
       </c>
       <c r="G3" t="n">
         <v>3.3359</v>
@@ -688,13 +688,13 @@
         <v>1.7626</v>
       </c>
       <c r="S3" t="n">
-        <v>2.7728</v>
+        <v>1.9979</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8169</v>
+        <v>0.7904</v>
       </c>
       <c r="U3" t="n">
-        <v>1.9559</v>
+        <v>1.2075</v>
       </c>
       <c r="V3" t="n">
         <v>0.2754</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.9654</v>
+        <v>4.8619</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0906</v>
+        <v>0.5594</v>
       </c>
       <c r="F4" t="n">
-        <v>3.8748</v>
+        <v>4.3025</v>
       </c>
       <c r="G4" t="n">
         <v>3.1763</v>
@@ -766,13 +766,13 @@
         <v>1.9585</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.1693</v>
+        <v>-0.2729</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6952</v>
+        <v>-0.2264</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4742</v>
+        <v>-0.0465</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. RUMSHA</t>
+          <t>A. GOMEZ VAZQUEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.926</v>
+        <v>2.7183</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5825</v>
+        <v>-1.2871</v>
       </c>
       <c r="F5" t="n">
-        <v>3.5085</v>
+        <v>4.0054</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5942</v>
+        <v>2.7431</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.2809</v>
+        <v>1.0605</v>
       </c>
       <c r="I5" t="n">
-        <v>2.875</v>
+        <v>1.6826</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.7973</v>
+        <v>0.285</v>
       </c>
       <c r="K5" t="n">
-        <v>-2.4892</v>
+        <v>0.2398</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6919</v>
+        <v>0.0452</v>
       </c>
       <c r="M5" t="n">
-        <v>2.3915</v>
+        <v>2.4581</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2083</v>
+        <v>0.8208</v>
       </c>
       <c r="O5" t="n">
-        <v>2.1832</v>
+        <v>1.6374</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7834</v>
+        <v>-0.7834</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9792</v>
+        <v>-1.9585</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7626</v>
+        <v>1.1751</v>
       </c>
       <c r="S5" t="n">
-        <v>1.5484</v>
+        <v>0.7585</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9775</v>
+        <v>0.3864</v>
       </c>
       <c r="U5" t="n">
-        <v>0.571</v>
+        <v>0.3721</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2166</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2166</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. GOMEZ VAZQUEZ</t>
+          <t>G. RUMSHA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.3754</v>
+        <v>2.3865</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.3894</v>
+        <v>-1.2823</v>
       </c>
       <c r="F6" t="n">
-        <v>3.7648</v>
+        <v>3.6689</v>
       </c>
       <c r="G6" t="n">
-        <v>2.7431</v>
+        <v>0.5942</v>
       </c>
       <c r="H6" t="n">
-        <v>1.0605</v>
+        <v>-2.2809</v>
       </c>
       <c r="I6" t="n">
-        <v>1.6826</v>
+        <v>2.875</v>
       </c>
       <c r="J6" t="n">
-        <v>0.285</v>
+        <v>-1.7973</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2398</v>
+        <v>-2.4892</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0452</v>
+        <v>0.6919</v>
       </c>
       <c r="M6" t="n">
-        <v>2.4581</v>
+        <v>2.3915</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8208</v>
+        <v>0.2083</v>
       </c>
       <c r="O6" t="n">
-        <v>1.6374</v>
+        <v>2.1832</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.7834</v>
+        <v>0.7834</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9585</v>
+        <v>-0.9792</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1751</v>
+        <v>1.7626</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4156</v>
+        <v>1.0089</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2841</v>
+        <v>0.2776</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1316</v>
+        <v>0.7314000000000001</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.2166</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4747</v>
+        <v>0.4469</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.8018</v>
+        <v>-2.99</v>
       </c>
       <c r="F7" t="n">
-        <v>3.2766</v>
+        <v>3.4369</v>
       </c>
       <c r="G7" t="n">
         <v>-0.6864</v>
@@ -1000,13 +1000,13 @@
         <v>1.1751</v>
       </c>
       <c r="S7" t="n">
-        <v>1.6496</v>
+        <v>1.6218</v>
       </c>
       <c r="T7" t="n">
-        <v>1.0545</v>
+        <v>0.8663</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5951</v>
+        <v>0.7554999999999999</v>
       </c>
       <c r="V7" t="n">
         <v>1.2742</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2491</v>
+        <v>0.3026</v>
       </c>
       <c r="E8" t="n">
         <v>-0.0594</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3085</v>
+        <v>0.362</v>
       </c>
       <c r="G8" t="n">
         <v>0.2729</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0238</v>
+        <v>0.0297</v>
       </c>
       <c r="T8" t="n">
         <v>-0.0594</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0356</v>
+        <v>0.0891</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8923</v>
+        <v>-0.2734</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.612</v>
+        <v>-3.1268</v>
       </c>
       <c r="F9" t="n">
-        <v>2.7197</v>
+        <v>2.8534</v>
       </c>
       <c r="G9" t="n">
         <v>0.8054</v>
@@ -1156,13 +1156,13 @@
         <v>1.5668</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3267</v>
+        <v>0.2922</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4464</v>
+        <v>0.0388</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1197</v>
+        <v>0.2533</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0255</v>
+        <v>-1.4297</v>
       </c>
       <c r="E10" t="n">
-        <v>-6.5844</v>
+        <v>-6.3203</v>
       </c>
       <c r="F10" t="n">
-        <v>5.5588</v>
+        <v>4.8906</v>
       </c>
       <c r="G10" t="n">
         <v>-2.2671</v>
@@ -1234,13 +1234,13 @@
         <v>1.5668</v>
       </c>
       <c r="S10" t="n">
-        <v>1.3959</v>
+        <v>0.9917</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1317</v>
+        <v>0.1323</v>
       </c>
       <c r="U10" t="n">
-        <v>1.5277</v>
+        <v>0.8594000000000001</v>
       </c>
       <c r="V10" t="n">
         <v>1.2166</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.4946</v>
+        <v>-3.3922</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.9563</v>
+        <v>-2.854</v>
       </c>
       <c r="F11" t="n">
         <v>-0.5383</v>
@@ -1312,10 +1312,10 @@
         <v>0.7834</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1958</v>
+        <v>-0.0935</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3564</v>
+        <v>-0.2541</v>
       </c>
       <c r="U11" t="n">
         <v>0.1606</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>17.0839</v>
+        <v>17.975</v>
       </c>
       <c r="E12" t="n">
-        <v>-19.5513</v>
+        <v>-18.6602</v>
       </c>
       <c r="F12" t="n">
         <v>36.6352</v>
@@ -1381,7 +1381,7 @@
         <v>15.7174</v>
       </c>
       <c r="P12" t="n">
-        <v>-3.916800000000001</v>
+        <v>-3.9168</v>
       </c>
       <c r="Q12" t="n">
         <v>-17.6263</v>
@@ -1390,13 +1390,13 @@
         <v>13.7094</v>
       </c>
       <c r="S12" t="n">
-        <v>6.3812</v>
+        <v>7.2722</v>
       </c>
       <c r="T12" t="n">
-        <v>1.3233</v>
+        <v>2.2142</v>
       </c>
       <c r="U12" t="n">
-        <v>5.0581</v>
+        <v>5.058</v>
       </c>
       <c r="V12" t="n">
         <v>2.7662</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.41</v>
+        <v>5.416</v>
       </c>
       <c r="E13" t="n">
-        <v>2.8609</v>
+        <v>1.4282</v>
       </c>
       <c r="F13" t="n">
-        <v>4.5492</v>
+        <v>3.9878</v>
       </c>
       <c r="G13" t="n">
         <v>2.6087</v>
@@ -1468,13 +1468,13 @@
         <v>3.3294</v>
       </c>
       <c r="S13" t="n">
-        <v>1.4719</v>
+        <v>-0.5221</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7687</v>
+        <v>-0.664</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7032</v>
+        <v>0.1419</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.9909</v>
+        <v>1.8692</v>
       </c>
       <c r="E14" t="n">
-        <v>0.7812</v>
+        <v>0.5765</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2097</v>
+        <v>1.2927</v>
       </c>
       <c r="G14" t="n">
         <v>1.8548</v>
@@ -1546,13 +1546,13 @@
         <v>1.3709</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7236</v>
+        <v>0.602</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4911</v>
+        <v>0.2864</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2326</v>
+        <v>0.3155</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5492</v>
+        <v>0.6294</v>
       </c>
       <c r="E15" t="n">
         <v>-0.1782</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7274</v>
+        <v>0.8076</v>
       </c>
       <c r="G15" t="n">
         <v>0.6145</v>
@@ -1624,13 +1624,13 @@
         <v>0.1958</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2612</v>
+        <v>-0.181</v>
       </c>
       <c r="T15" t="n">
         <v>-0.1782</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.083</v>
+        <v>-0.0028</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. FERNANDEZ LOPEZ</t>
+          <t>I. SAMA PEREZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.101</v>
+        <v>-0.0373</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1188</v>
+        <v>-4.714</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0178</v>
+        <v>4.6767</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>-0.2689</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>0.176</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>-0.4449</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>-1.7239</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>-0.1719</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>-1.5521</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1.455</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>0.3479</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.1072</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.1751</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.9585</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>3.1336</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.101</v>
+        <v>-0.9435</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1188</v>
+        <v>-1.0316</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0178</v>
+        <v>0.0881</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. SAMA PEREZ</t>
+          <t>M. FERNANDEZ LOPEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3868</v>
+        <v>-0.0743</v>
       </c>
       <c r="E17" t="n">
-        <v>-5.328</v>
+        <v>-0.1188</v>
       </c>
       <c r="F17" t="n">
-        <v>4.9412</v>
+        <v>0.0446</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.2689</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.176</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4449</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.7239</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.1719</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.5521</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.455</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0.3479</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>1.1072</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1751</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9585</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>3.1336</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.293</v>
+        <v>-0.0743</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.6456</v>
+        <v>-0.1188</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3526</v>
+        <v>0.0446</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.8756</v>
+        <v>-2.2229</v>
       </c>
       <c r="E18" t="n">
-        <v>-4.2839</v>
+        <v>-3.8745</v>
       </c>
       <c r="F18" t="n">
-        <v>1.4082</v>
+        <v>1.6516</v>
       </c>
       <c r="G18" t="n">
         <v>-1.9449</v>
@@ -1858,13 +1858,13 @@
         <v>0.9792</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.5967</v>
+        <v>-0.944</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8734</v>
+        <v>-0.464</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7233000000000001</v>
+        <v>-0.4799</v>
       </c>
       <c r="V18" t="n">
         <v>0.6659</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.416</v>
+        <v>-2.3715</v>
       </c>
       <c r="E19" t="n">
-        <v>-6.1207</v>
+        <v>-5.5067</v>
       </c>
       <c r="F19" t="n">
-        <v>2.7047</v>
+        <v>3.1352</v>
       </c>
       <c r="G19" t="n">
         <v>-2.4923</v>
@@ -1936,13 +1936,13 @@
         <v>2.1543</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.3949</v>
+        <v>-0.3504</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.111</v>
+        <v>-0.497</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2839</v>
+        <v>0.1466</v>
       </c>
       <c r="V19" t="n">
         <v>0.2754</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.9174</v>
+        <v>-4.0289</v>
       </c>
       <c r="E20" t="n">
-        <v>-5.7242</v>
+        <v>-5.6219</v>
       </c>
       <c r="F20" t="n">
-        <v>1.8068</v>
+        <v>1.593</v>
       </c>
       <c r="G20" t="n">
         <v>-3.2708</v>
@@ -2014,13 +2014,13 @@
         <v>0.9792</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6466</v>
+        <v>-0.7581</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7128</v>
+        <v>-0.6105</v>
       </c>
       <c r="U20" t="n">
-        <v>0.06619999999999999</v>
+        <v>-0.1476</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. HERMIDA PEREZ</t>
+          <t>P. FERNANDEZ GONZALEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.2105</v>
+        <v>-4.8607</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.9457</v>
+        <v>-5.9848</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7353</v>
+        <v>1.124</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.4041</v>
+        <v>-3.2123</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.5043</v>
+        <v>-0.4029</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.8999</v>
+        <v>-2.8094</v>
       </c>
       <c r="J21" t="n">
-        <v>-5.3966</v>
+        <v>-3.7111</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.6677</v>
+        <v>-0.3404</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.7289</v>
+        <v>-3.3708</v>
       </c>
       <c r="M21" t="n">
-        <v>1.9925</v>
+        <v>0.4989</v>
       </c>
       <c r="N21" t="n">
-        <v>1.1634</v>
+        <v>-0.0625</v>
       </c>
       <c r="O21" t="n">
-        <v>0.8290999999999999</v>
+        <v>0.5614</v>
       </c>
       <c r="P21" t="n">
-        <v>1.1751</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9792</v>
+        <v>-1.9585</v>
       </c>
       <c r="R21" t="n">
-        <v>2.1543</v>
+        <v>1.7626</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0989</v>
+        <v>-0.236</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1206</v>
+        <v>-0.5905</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.9784</v>
+        <v>0.3545</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.8825</v>
+        <v>-1.2166</v>
       </c>
       <c r="W21" t="n">
-        <v>0.5507</v>
+        <v>0.2754</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.4332</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.3091</v>
+        <v>-5.1948</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.8764</v>
+        <v>-5.9787</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5673</v>
+        <v>0.784</v>
       </c>
       <c r="G22" t="n">
         <v>-2.3382</v>
@@ -2170,13 +2170,13 @@
         <v>1.5668</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9917</v>
+        <v>-0.8774</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2506</v>
+        <v>-0.3529</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7411</v>
+        <v>-0.5245</v>
       </c>
       <c r="V22" t="n">
         <v>-0.6083</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P. FERNANDEZ GONZALEZ</t>
+          <t>A. HERMIDA PEREZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.8177</v>
+        <v>-5.5259</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.7011</v>
+        <v>-6.6621</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8835</v>
+        <v>1.1362</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.2123</v>
+        <v>-3.4041</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.4029</v>
+        <v>-1.5043</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.8094</v>
+        <v>-1.8999</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.7111</v>
+        <v>-5.3966</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.3404</v>
+        <v>-2.6677</v>
       </c>
       <c r="L23" t="n">
-        <v>-3.3708</v>
+        <v>-2.7289</v>
       </c>
       <c r="M23" t="n">
-        <v>0.4989</v>
+        <v>1.9925</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.0625</v>
+        <v>1.1634</v>
       </c>
       <c r="O23" t="n">
-        <v>0.5614</v>
+        <v>0.8290999999999999</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.1958</v>
+        <v>1.1751</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.9585</v>
+        <v>-0.9792</v>
       </c>
       <c r="R23" t="n">
-        <v>1.7626</v>
+        <v>2.1543</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1929</v>
+        <v>-1.4143</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.3068</v>
+        <v>-0.8369</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1139</v>
+        <v>-0.5774</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.2166</v>
+        <v>-1.8825</v>
       </c>
       <c r="W23" t="n">
-        <v>0.2754</v>
+        <v>0.5507</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.492</v>
+        <v>-2.4332</v>
       </c>
     </row>
     <row r="24">
@@ -2281,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-17.084</v>
+        <v>-16.4017</v>
       </c>
       <c r="E24" t="n">
-        <v>-36.6349</v>
+        <v>-36.635</v>
       </c>
       <c r="F24" t="n">
-        <v>19.5511</v>
+        <v>20.2334</v>
       </c>
       <c r="G24" t="n">
         <v>-11.8535</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.3801</v>
+        <v>-2.380100000000001</v>
       </c>
       <c r="I24" t="n">
         <v>-9.4734</v>
@@ -2314,10 +2314,10 @@
         <v>2.0882</v>
       </c>
       <c r="O24" t="n">
-        <v>6.243900000000001</v>
+        <v>6.2439</v>
       </c>
       <c r="P24" t="n">
-        <v>3.917000000000001</v>
+        <v>3.917</v>
       </c>
       <c r="Q24" t="n">
         <v>-13.7093</v>
@@ -2326,13 +2326,13 @@
         <v>17.6261</v>
       </c>
       <c r="S24" t="n">
-        <v>-6.3814</v>
+        <v>-5.6991</v>
       </c>
       <c r="T24" t="n">
         <v>-5.058</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.3234</v>
+        <v>-0.641</v>
       </c>
       <c r="V24" t="n">
         <v>-2.7661</v>
